--- a/Model_zzy/results_ro.xlsx
+++ b/Model_zzy/results_ro.xlsx
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1702.82327902657</v>
+        <v>1702.823279026571</v>
       </c>
     </row>
     <row r="27">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1694.906038484885</v>
+        <v>1694.906038484886</v>
       </c>
     </row>
     <row r="28">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2524.028948764597</v>
+        <v>2524.028948764598</v>
       </c>
     </row>
     <row r="34">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2620.610328957299</v>
+        <v>2620.6103289573</v>
       </c>
     </row>
     <row r="36">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2623.572526260096</v>
+        <v>2623.572526260095</v>
       </c>
     </row>
     <row r="47">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3094.242541155741</v>
+        <v>3094.24254115574</v>
       </c>
     </row>
     <row r="50">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>16.01979971787171</v>
+        <v>16.01979971787154</v>
       </c>
     </row>
     <row r="101">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>120.6887997178717</v>
+        <v>120.6887997178715</v>
       </c>
     </row>
     <row r="102">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>225.3577997178717</v>
+        <v>225.3577997178715</v>
       </c>
     </row>
     <row r="103">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>330.0267997178717</v>
+        <v>330.0267997178715</v>
       </c>
     </row>
     <row r="104">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-213.8548000000001</v>
+        <v>-213.8548</v>
       </c>
     </row>
     <row r="107">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-320.7822000000001</v>
+        <v>-320.7822</v>
       </c>
     </row>
     <row r="108">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-427.7096000000001</v>
+        <v>-427.7096</v>
       </c>
     </row>
     <row r="109">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-534.6370000000002</v>
+        <v>-534.6370000000001</v>
       </c>
     </row>
     <row r="110">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>314.007</v>
+        <v>314.0069999999999</v>
       </c>
     </row>
     <row r="113">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>418.676</v>
+        <v>418.6759999999999</v>
       </c>
     </row>
     <row r="114">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>523.345</v>
+        <v>523.3449999999999</v>
       </c>
     </row>
     <row r="115">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-213.8548</v>
+        <v>-213.8547999999999</v>
       </c>
     </row>
     <row r="117">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-320.7822</v>
+        <v>-320.7821999999999</v>
       </c>
     </row>
     <row r="118">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-403.6238171567549</v>
+        <v>-403.6238171567556</v>
       </c>
     </row>
     <row r="119">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1010.421819746084</v>
+        <v>1010.421819746085</v>
       </c>
     </row>
     <row r="125">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>798.3395030402431</v>
+        <v>798.3395030402434</v>
       </c>
     </row>
     <row r="133">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>202.7017129230513</v>
+        <v>202.7017129230517</v>
       </c>
     </row>
     <row r="134">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>296.4984094972052</v>
+        <v>296.4984094972056</v>
       </c>
     </row>
     <row r="135">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>484.3096126782108</v>
+        <v>484.3096126782111</v>
       </c>
     </row>
     <row r="136">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>765.9472934528544</v>
+        <v>765.9472934528546</v>
       </c>
     </row>
     <row r="137">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>888.4121039147632</v>
+        <v>888.4121039147642</v>
       </c>
     </row>
     <row r="142">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>16.01979971787171</v>
+        <v>16.01979971787154</v>
       </c>
     </row>
     <row r="149">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>120.6887997178717</v>
+        <v>120.6887997178715</v>
       </c>
     </row>
     <row r="150">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>225.3577997178717</v>
+        <v>225.3577997178715</v>
       </c>
     </row>
     <row r="151">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>330.0267997178717</v>
+        <v>330.0267997178715</v>
       </c>
     </row>
     <row r="152">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>314.007</v>
+        <v>314.0069999999999</v>
       </c>
     </row>
     <row r="161">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>418.676</v>
+        <v>418.6759999999999</v>
       </c>
     </row>
     <row r="162">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>523.345</v>
+        <v>523.3449999999999</v>
       </c>
     </row>
     <row r="163">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>213.8548000000001</v>
+        <v>213.8548</v>
       </c>
     </row>
     <row r="179">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>320.7822000000001</v>
+        <v>320.7822</v>
       </c>
     </row>
     <row r="180">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>427.7096000000001</v>
+        <v>427.7096</v>
       </c>
     </row>
     <row r="181">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>534.6370000000002</v>
+        <v>534.6370000000001</v>
       </c>
     </row>
     <row r="182">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>213.8548</v>
+        <v>213.8547999999999</v>
       </c>
     </row>
     <row r="189">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>320.7822</v>
+        <v>320.7821999999999</v>
       </c>
     </row>
     <row r="190">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>403.6238171567549</v>
+        <v>403.6238171567556</v>
       </c>
     </row>
     <row r="191">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>2.122645472839639e-16</v>
       </c>
     </row>
     <row r="212">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-0</v>
+        <v>2.122645472839639e-16</v>
       </c>
     </row>
     <row r="213">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>2.122645472839639e-16</v>
       </c>
     </row>
     <row r="214">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>2.122645472839639e-16</v>
       </c>
     </row>
     <row r="215">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>79.01921061712554</v>
+        <v>79.01921061712552</v>
       </c>
     </row>
     <row r="220">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>83.41228582879998</v>
+        <v>83.41228582879997</v>
       </c>
     </row>
     <row r="307">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>73.82499321319999</v>
+        <v>73.82499321319997</v>
       </c>
     </row>
     <row r="310">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="332">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="336">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>73.24864608059539</v>
+        <v>73.24864608059536</v>
       </c>
     </row>
     <row r="365">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>196.5508205246116</v>
+        <v>196.5508205246115</v>
       </c>
     </row>
     <row r="368">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>56.50505660651769</v>
+        <v>56.5050566065177</v>
       </c>
     </row>
     <row r="378">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>73.24864608059539</v>
+        <v>73.24864608059536</v>
       </c>
     </row>
     <row r="389">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>196.5508205246116</v>
+        <v>196.5508205246115</v>
       </c>
     </row>
     <row r="392">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>56.50505660651769</v>
+        <v>56.5050566065177</v>
       </c>
     </row>
     <row r="402">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>399.1827715358338</v>
+        <v>399.1827715358341</v>
       </c>
     </row>
     <row r="411">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>398.8327715358337</v>
+        <v>398.832771535834</v>
       </c>
     </row>
     <row r="412">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>398.4827715358337</v>
+        <v>398.482771535834</v>
       </c>
     </row>
     <row r="413">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>398.1327715358337</v>
+        <v>398.132771535834</v>
       </c>
     </row>
     <row r="414">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>397.7827715358335</v>
+        <v>397.7827715358338</v>
       </c>
     </row>
     <row r="415">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>397.4327715358335</v>
+        <v>397.4327715358339</v>
       </c>
     </row>
     <row r="416">
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>397.0827715358337</v>
+        <v>397.082771535834</v>
       </c>
     </row>
     <row r="417">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>396.7327715358337</v>
+        <v>396.732771535834</v>
       </c>
     </row>
     <row r="418">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>396.3827715358336</v>
+        <v>396.3827715358339</v>
       </c>
     </row>
     <row r="419">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>396.0327715358336</v>
+        <v>396.0327715358339</v>
       </c>
     </row>
     <row r="420">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>395.6827715358335</v>
+        <v>395.6827715358338</v>
       </c>
     </row>
     <row r="421">
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>395.3327715358336</v>
+        <v>395.3327715358338</v>
       </c>
     </row>
     <row r="422">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>395.3327715358337</v>
+        <v>395.3327715358336</v>
       </c>
     </row>
     <row r="426">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>394.9827715358336</v>
+        <v>394.9827715358335</v>
       </c>
     </row>
     <row r="427">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>393.9327715358336</v>
+        <v>393.9327715358335</v>
       </c>
     </row>
     <row r="430">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>393.5827715358337</v>
+        <v>393.5827715358336</v>
       </c>
     </row>
     <row r="431">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>393.2327715358337</v>
+        <v>393.2327715358336</v>
       </c>
     </row>
     <row r="432">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>393.5827715358337</v>
+        <v>393.5827715358336</v>
       </c>
     </row>
     <row r="433">
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>393.9327715358336</v>
+        <v>393.9327715358335</v>
       </c>
     </row>
     <row r="434">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>399.1827715358338</v>
+        <v>399.1827715358341</v>
       </c>
     </row>
     <row r="435">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>398.8327715358337</v>
+        <v>398.832771535834</v>
       </c>
     </row>
     <row r="436">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>398.4827715358337</v>
+        <v>398.482771535834</v>
       </c>
     </row>
     <row r="437">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>398.1327715358337</v>
+        <v>398.132771535834</v>
       </c>
     </row>
     <row r="438">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>397.7827715358335</v>
+        <v>397.7827715358338</v>
       </c>
     </row>
     <row r="439">
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>397.4327715358335</v>
+        <v>397.4327715358339</v>
       </c>
     </row>
     <row r="440">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>397.0827715358337</v>
+        <v>397.082771535834</v>
       </c>
     </row>
     <row r="441">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>396.7327715358337</v>
+        <v>396.732771535834</v>
       </c>
     </row>
     <row r="442">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>396.3827715358336</v>
+        <v>396.3827715358339</v>
       </c>
     </row>
     <row r="443">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>396.0327715358336</v>
+        <v>396.0327715358339</v>
       </c>
     </row>
     <row r="444">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>395.6827715358335</v>
+        <v>395.6827715358338</v>
       </c>
     </row>
     <row r="445">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>395.3327715358336</v>
+        <v>395.3327715358338</v>
       </c>
     </row>
     <row r="446">
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>395.3327715358337</v>
+        <v>395.3327715358336</v>
       </c>
     </row>
     <row r="450">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>394.9827715358336</v>
+        <v>394.9827715358335</v>
       </c>
     </row>
     <row r="451">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>393.9327715358336</v>
+        <v>393.9327715358335</v>
       </c>
     </row>
     <row r="454">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>393.5827715358337</v>
+        <v>393.5827715358336</v>
       </c>
     </row>
     <row r="455">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>393.2327715358337</v>
+        <v>393.2327715358336</v>
       </c>
     </row>
     <row r="456">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>393.5827715358337</v>
+        <v>393.5827715358336</v>
       </c>
     </row>
     <row r="457">
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>393.9327715358336</v>
+        <v>393.9327715358335</v>
       </c>
     </row>
     <row r="458">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>38.16979232317365</v>
+        <v>38.16979232317362</v>
       </c>
     </row>
     <row r="533">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>90.50429232317366</v>
+        <v>90.50429232317362</v>
       </c>
     </row>
     <row r="534">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>142.8387923231737</v>
+        <v>142.8387923231736</v>
       </c>
     </row>
     <row r="535">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>195.1732923231737</v>
+        <v>195.1732923231736</v>
       </c>
     </row>
     <row r="536">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>8.963195702659297</v>
+        <v>8.963195702659306</v>
       </c>
     </row>
     <row r="546">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>510.7358338585389</v>
+        <v>510.735833858539</v>
       </c>
     </row>
     <row r="557">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>572.924551039907</v>
+        <v>572.9245510399071</v>
       </c>
     </row>
     <row r="558">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>406.8164625283683</v>
+        <v>406.8164625283684</v>
       </c>
     </row>
     <row r="574">
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>38.16979232317365</v>
+        <v>38.16979232317362</v>
       </c>
     </row>
     <row r="581">
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>90.50429232317366</v>
+        <v>90.50429232317362</v>
       </c>
     </row>
     <row r="582">
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>142.8387923231737</v>
+        <v>142.8387923231736</v>
       </c>
     </row>
     <row r="583">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>195.1732923231737</v>
+        <v>195.1732923231736</v>
       </c>
     </row>
     <row r="584">
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>8.963195702659297</v>
+        <v>8.963195702659306</v>
       </c>
     </row>
     <row r="594">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>4.316420985038163</v>
+        <v>4.316420985038164</v>
       </c>
     </row>
     <row r="655">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="664">
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>5.335455642281759</v>
+        <v>5.33545564228176</v>
       </c>
     </row>
     <row r="676">
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>5.236579626690985</v>
+        <v>5.236579626690986</v>
       </c>
     </row>
     <row r="677">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>6.260083570748989</v>
+        <v>6.260083570748996</v>
       </c>
     </row>
     <row r="689">
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>4.027157958642411</v>
+        <v>4.027157958642412</v>
       </c>
     </row>
     <row r="693">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="713">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="737">
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>73.24864608059539</v>
+        <v>73.24864608059536</v>
       </c>
     </row>
     <row r="773">
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>196.5508205246116</v>
+        <v>196.5508205246115</v>
       </c>
     </row>
     <row r="776">
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>56.50505660651769</v>
+        <v>56.5050566065177</v>
       </c>
     </row>
     <row r="786">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>91.56080760074424</v>
+        <v>91.5608076007442</v>
       </c>
     </row>
     <row r="797">
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>194.3729149311936</v>
+        <v>194.3729149311935</v>
       </c>
     </row>
     <row r="799">
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>245.6885256557645</v>
+        <v>245.6885256557644</v>
       </c>
     </row>
     <row r="800">
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>291.6037446595245</v>
+        <v>291.6037446595244</v>
       </c>
     </row>
     <row r="801">
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>91.56080760074424</v>
+        <v>91.5608076007442</v>
       </c>
     </row>
     <row r="941">
@@ -9837,7 +9837,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>142.9455999126178</v>
+        <v>142.9455999126177</v>
       </c>
     </row>
     <row r="942">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>245.6885256557645</v>
+        <v>245.6885256557644</v>
       </c>
     </row>
     <row r="944">
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>291.6037446595245</v>
+        <v>291.6037446595244</v>
       </c>
     </row>
     <row r="945">
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>70.63132075814711</v>
+        <v>70.63132075814713</v>
       </c>
     </row>
     <row r="954">
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>91.56080760074424</v>
+        <v>91.5608076007442</v>
       </c>
     </row>
     <row r="965">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>142.9455999126178</v>
+        <v>142.9455999126177</v>
       </c>
     </row>
     <row r="966">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>245.6885256557645</v>
+        <v>245.6885256557644</v>
       </c>
     </row>
     <row r="968">
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>291.6037446595245</v>
+        <v>291.6037446595244</v>
       </c>
     </row>
     <row r="969">
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>70.63132075814711</v>
+        <v>70.63132075814713</v>
       </c>
     </row>
     <row r="978">
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>12.54967139066454</v>
+        <v>12.54967139066457</v>
       </c>
     </row>
     <row r="1012">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>117.2186713906645</v>
+        <v>117.2186713906646</v>
       </c>
     </row>
     <row r="1013">
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>221.8876713906645</v>
+        <v>221.8876713906646</v>
       </c>
     </row>
     <row r="1014">
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>326.5566713906645</v>
+        <v>326.5566713906646</v>
       </c>
     </row>
     <row r="1015">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>345.0231996956444</v>
+        <v>345.0231996956447</v>
       </c>
     </row>
     <row r="1016">
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>287.7493447763995</v>
+        <v>287.7493447763997</v>
       </c>
     </row>
     <row r="1017">
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>-57.99874786331274</v>
+        <v>-57.9987478633125</v>
       </c>
     </row>
     <row r="1021">
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>-135.216555739458</v>
+        <v>-135.2165557394579</v>
       </c>
     </row>
     <row r="1022">
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>-89.64833769115738</v>
+        <v>-89.64833769115742</v>
       </c>
     </row>
     <row r="1025">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>-124.4285373215637</v>
+        <v>-124.4285373215638</v>
       </c>
     </row>
     <row r="1027">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>-11.13261648897842</v>
+        <v>-11.13261648897855</v>
       </c>
     </row>
     <row r="1029">
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>34.72893651189274</v>
+        <v>34.72893651189268</v>
       </c>
     </row>
     <row r="1030">
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>56.70879471515894</v>
+        <v>56.70879471515885</v>
       </c>
     </row>
     <row r="1031">
@@ -10737,7 +10737,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>75.07073656049496</v>
+        <v>75.07073656049488</v>
       </c>
     </row>
     <row r="1032">
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>88.75360540350613</v>
+        <v>88.75360540350601</v>
       </c>
     </row>
     <row r="1033">
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>193.4226054035062</v>
+        <v>193.422605403506</v>
       </c>
     </row>
     <row r="1034">
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>1511.548746934868</v>
+        <v>1511.548746934867</v>
       </c>
     </row>
     <row r="1039">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>1782.145235472143</v>
+        <v>1782.145235472142</v>
       </c>
     </row>
     <row r="1040">
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>1628.144390160872</v>
+        <v>1628.144390160873</v>
       </c>
     </row>
     <row r="1046">
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>1433.172305045687</v>
+        <v>1433.172305045688</v>
       </c>
     </row>
     <row r="1047">
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>1128.366635048758</v>
+        <v>1128.366635048759</v>
       </c>
     </row>
     <row r="1049">
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>962.4952790035978</v>
+        <v>962.4952790035987</v>
       </c>
     </row>
     <row r="1050">
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>801.6713353225872</v>
+        <v>801.6713353225874</v>
       </c>
     </row>
     <row r="1051">
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>698.1892145151662</v>
+        <v>698.1892145151664</v>
       </c>
     </row>
     <row r="1052">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>674.6191804280521</v>
+        <v>674.6191804280526</v>
       </c>
     </row>
     <row r="1053">
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>694.0194887567402</v>
+        <v>694.0194887567404</v>
       </c>
     </row>
     <row r="1054">
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>731.8116719332742</v>
+        <v>731.8116719332745</v>
       </c>
     </row>
     <row r="1055">
@@ -10977,7 +10977,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>784.6446229306957</v>
+        <v>784.644622930696</v>
       </c>
     </row>
     <row r="1056">
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>848.3155181797155</v>
+        <v>848.3155181797157</v>
       </c>
     </row>
     <row r="1057">
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>12.54967139066454</v>
+        <v>12.54967139066457</v>
       </c>
     </row>
     <row r="1060">
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>117.2186713906645</v>
+        <v>117.2186713906646</v>
       </c>
     </row>
     <row r="1061">
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>221.8876713906645</v>
+        <v>221.8876713906646</v>
       </c>
     </row>
     <row r="1062">
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>326.5566713906645</v>
+        <v>326.5566713906646</v>
       </c>
     </row>
     <row r="1063">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>345.0231996956444</v>
+        <v>345.0231996956447</v>
       </c>
     </row>
     <row r="1064">
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>287.7493447763995</v>
+        <v>287.7493447763997</v>
       </c>
     </row>
     <row r="1065">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>34.72893651189274</v>
+        <v>34.72893651189268</v>
       </c>
     </row>
     <row r="1078">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>56.70879471515894</v>
+        <v>56.70879471515885</v>
       </c>
     </row>
     <row r="1079">
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>75.07073656049496</v>
+        <v>75.07073656049488</v>
       </c>
     </row>
     <row r="1080">
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>88.75360540350613</v>
+        <v>88.75360540350601</v>
       </c>
     </row>
     <row r="1081">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>193.4226054035062</v>
+        <v>193.422605403506</v>
       </c>
     </row>
     <row r="1082">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>57.99874786331274</v>
+        <v>57.9987478633125</v>
       </c>
     </row>
     <row r="1093">
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>135.216555739458</v>
+        <v>135.2165557394579</v>
       </c>
     </row>
     <row r="1094">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>89.64833769115738</v>
+        <v>89.64833769115742</v>
       </c>
     </row>
     <row r="1097">
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>124.4285373215637</v>
+        <v>124.4285373215638</v>
       </c>
     </row>
     <row r="1099">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>11.13261648897842</v>
+        <v>11.13261648897855</v>
       </c>
     </row>
     <row r="1101">
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>1</v>
+        <v>0.9999999999999981</v>
       </c>
     </row>
     <row r="1126">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="1161">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1204">
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="1221">
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>1</v>
+        <v>0.9999999999999981</v>
       </c>
     </row>
     <row r="1246">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>-0</v>
+        <v>1.887379141862766e-15</v>
       </c>
     </row>
     <row r="1247">
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>399.1827715358338</v>
+        <v>399.1827715358341</v>
       </c>
     </row>
     <row r="1275">
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>398.8327715358337</v>
+        <v>398.832771535834</v>
       </c>
     </row>
     <row r="1276">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>398.4827715358337</v>
+        <v>398.482771535834</v>
       </c>
     </row>
     <row r="1277">
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>398.1327715358337</v>
+        <v>398.132771535834</v>
       </c>
     </row>
     <row r="1278">
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>397.7827715358335</v>
+        <v>397.7827715358338</v>
       </c>
     </row>
     <row r="1279">
@@ -13217,7 +13217,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>397.4327715358335</v>
+        <v>397.4327715358339</v>
       </c>
     </row>
     <row r="1280">
@@ -13227,7 +13227,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>397.0827715358337</v>
+        <v>397.082771535834</v>
       </c>
     </row>
     <row r="1281">
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>396.7327715358337</v>
+        <v>396.732771535834</v>
       </c>
     </row>
     <row r="1282">
@@ -13247,7 +13247,7 @@
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>396.3827715358336</v>
+        <v>396.3827715358339</v>
       </c>
     </row>
     <row r="1283">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>396.0327715358336</v>
+        <v>396.0327715358339</v>
       </c>
     </row>
     <row r="1284">
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>395.6827715358335</v>
+        <v>395.6827715358338</v>
       </c>
     </row>
     <row r="1285">
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>395.3327715358336</v>
+        <v>395.3327715358338</v>
       </c>
     </row>
     <row r="1286">
@@ -13317,7 +13317,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>395.3327715358337</v>
+        <v>395.3327715358336</v>
       </c>
     </row>
     <row r="1290">
@@ -13327,7 +13327,7 @@
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>394.9827715358336</v>
+        <v>394.9827715358335</v>
       </c>
     </row>
     <row r="1291">
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>393.9327715358336</v>
+        <v>393.9327715358335</v>
       </c>
     </row>
     <row r="1294">
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>393.5827715358337</v>
+        <v>393.5827715358336</v>
       </c>
     </row>
     <row r="1295">
@@ -13377,7 +13377,7 @@
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>393.2327715358337</v>
+        <v>393.2327715358336</v>
       </c>
     </row>
     <row r="1296">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="B1296" t="n">
-        <v>393.5827715358337</v>
+        <v>393.5827715358336</v>
       </c>
     </row>
     <row r="1297">
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>393.9327715358336</v>
+        <v>393.9327715358335</v>
       </c>
     </row>
     <row r="1298">
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>339.3053558054587</v>
+        <v>339.305355805459</v>
       </c>
     </row>
     <row r="1299">
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>339.0078558054586</v>
+        <v>339.0078558054589</v>
       </c>
     </row>
     <row r="1300">
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>338.7103558054586</v>
+        <v>338.7103558054589</v>
       </c>
     </row>
     <row r="1301">
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>338.4128558054587</v>
+        <v>338.4128558054589</v>
       </c>
     </row>
     <row r="1302">
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>338.1153558054585</v>
+        <v>338.1153558054588</v>
       </c>
     </row>
     <row r="1303">
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>337.8178558054585</v>
+        <v>337.8178558054587</v>
       </c>
     </row>
     <row r="1304">
@@ -13467,7 +13467,7 @@
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>337.5203558054587</v>
+        <v>337.5203558054589</v>
       </c>
     </row>
     <row r="1305">
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>337.2228558054587</v>
+        <v>337.2228558054589</v>
       </c>
     </row>
     <row r="1306">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>336.9253558054585</v>
+        <v>336.9253558054588</v>
       </c>
     </row>
     <row r="1307">
@@ -13497,7 +13497,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>336.6278558054586</v>
+        <v>336.6278558054589</v>
       </c>
     </row>
     <row r="1308">
@@ -13507,7 +13507,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>336.3303558054585</v>
+        <v>336.3303558054587</v>
       </c>
     </row>
     <row r="1309">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>336.0328558054586</v>
+        <v>336.0328558054587</v>
       </c>
     </row>
     <row r="1310">
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>336.0328558054587</v>
+        <v>336.0328558054586</v>
       </c>
     </row>
     <row r="1312">
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>334.8428558054586</v>
+        <v>334.8428558054585</v>
       </c>
     </row>
     <row r="1318">
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>334.5453558054586</v>
+        <v>334.5453558054585</v>
       </c>
     </row>
     <row r="1319">
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>334.2478558054586</v>
+        <v>334.2478558054585</v>
       </c>
     </row>
     <row r="1320">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>334.5453558054587</v>
+        <v>334.5453558054585</v>
       </c>
     </row>
     <row r="1321">
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>334.8428558054586</v>
+        <v>334.8428558054584</v>
       </c>
     </row>
     <row r="1322">
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>186.13146458585</v>
+        <v>191.6009130600986</v>
       </c>
     </row>
     <row r="1359">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>67.75728283843742</v>
+        <v>67.7572828384374</v>
       </c>
     </row>
     <row r="1363">
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>92.44158188072224</v>
+        <v>92.44158188072221</v>
       </c>
     </row>
     <row r="1364">
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>78.7419230612546</v>
+        <v>78.74192306125461</v>
       </c>
     </row>
     <row r="1365">
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="B1366" t="n">
-        <v>81.12830487952854</v>
+        <v>88.63579658565527</v>
       </c>
     </row>
     <row r="1367">
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="B1382" t="n">
-        <v>10.295432422115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1383">
@@ -14487,7 +14487,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>158.2117448979725</v>
+        <v>162.8607761010838</v>
       </c>
     </row>
     <row r="1407">
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>57.5936904126718</v>
+        <v>57.59369041267179</v>
       </c>
     </row>
     <row r="1411">
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>78.5753445986139</v>
+        <v>78.57534459861388</v>
       </c>
     </row>
     <row r="1412">
@@ -14547,7 +14547,7 @@
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>66.93063460206641</v>
+        <v>66.93063460206642</v>
       </c>
     </row>
     <row r="1413">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>68.95905914759926</v>
+        <v>75.34042709780698</v>
       </c>
     </row>
     <row r="1415">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1430" t="n">
-        <v>8.751117558797752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1431">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>339.3053558054587</v>
+        <v>339.305355805459</v>
       </c>
     </row>
     <row r="1443">
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>339.0078558054586</v>
+        <v>339.0078558054589</v>
       </c>
     </row>
     <row r="1444">
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>338.7103558054586</v>
+        <v>338.7103558054589</v>
       </c>
     </row>
     <row r="1445">
@@ -14877,7 +14877,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>338.4128558054587</v>
+        <v>338.4128558054589</v>
       </c>
     </row>
     <row r="1446">
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>338.1153558054585</v>
+        <v>338.1153558054588</v>
       </c>
     </row>
     <row r="1447">
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>337.8178558054585</v>
+        <v>337.8178558054587</v>
       </c>
     </row>
     <row r="1448">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>337.5203558054587</v>
+        <v>337.5203558054589</v>
       </c>
     </row>
     <row r="1449">
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>337.2228558054587</v>
+        <v>337.2228558054589</v>
       </c>
     </row>
     <row r="1450">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>336.9253558054585</v>
+        <v>336.9253558054588</v>
       </c>
     </row>
     <row r="1451">
@@ -14937,7 +14937,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>336.6278558054586</v>
+        <v>336.6278558054589</v>
       </c>
     </row>
     <row r="1452">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>336.3303558054585</v>
+        <v>336.3303558054587</v>
       </c>
     </row>
     <row r="1453">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>336.0328558054586</v>
+        <v>336.0328558054587</v>
       </c>
     </row>
     <row r="1454">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>336.0328558054587</v>
+        <v>336.0328558054586</v>
       </c>
     </row>
     <row r="1456">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>334.8428558054586</v>
+        <v>334.8428558054585</v>
       </c>
     </row>
     <row r="1462">
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="B1462" t="n">
-        <v>334.5453558054586</v>
+        <v>334.5453558054585</v>
       </c>
     </row>
     <row r="1463">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>334.2478558054586</v>
+        <v>334.2478558054585</v>
       </c>
     </row>
     <row r="1464">
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="B1464" t="n">
-        <v>334.5453558054587</v>
+        <v>334.5453558054585</v>
       </c>
     </row>
     <row r="1465">
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>334.8428558054586</v>
+        <v>334.8428558054584</v>
       </c>
     </row>
     <row r="1466">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>339.3053558054587</v>
+        <v>339.305355805459</v>
       </c>
     </row>
     <row r="1467">
@@ -15097,7 +15097,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>339.0078558054586</v>
+        <v>339.0078558054589</v>
       </c>
     </row>
     <row r="1468">
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>338.7103558054586</v>
+        <v>338.7103558054589</v>
       </c>
     </row>
     <row r="1469">
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>338.4128558054587</v>
+        <v>338.4128558054589</v>
       </c>
     </row>
     <row r="1470">
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="B1470" t="n">
-        <v>338.1153558054585</v>
+        <v>338.1153558054588</v>
       </c>
     </row>
     <row r="1471">
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>337.8178558054585</v>
+        <v>337.8178558054587</v>
       </c>
     </row>
     <row r="1472">
@@ -15147,7 +15147,7 @@
         </is>
       </c>
       <c r="B1472" t="n">
-        <v>337.5203558054587</v>
+        <v>337.5203558054589</v>
       </c>
     </row>
     <row r="1473">
@@ -15157,7 +15157,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>337.2228558054587</v>
+        <v>337.2228558054589</v>
       </c>
     </row>
     <row r="1474">
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="B1474" t="n">
-        <v>336.9253558054585</v>
+        <v>336.9253558054588</v>
       </c>
     </row>
     <row r="1475">
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>336.6278558054586</v>
+        <v>336.6278558054589</v>
       </c>
     </row>
     <row r="1476">
@@ -15187,7 +15187,7 @@
         </is>
       </c>
       <c r="B1476" t="n">
-        <v>336.3303558054585</v>
+        <v>336.3303558054587</v>
       </c>
     </row>
     <row r="1477">
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>336.0328558054586</v>
+        <v>336.0328558054587</v>
       </c>
     </row>
     <row r="1478">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>336.0328558054587</v>
+        <v>336.0328558054586</v>
       </c>
     </row>
     <row r="1480">
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="B1485" t="n">
-        <v>334.8428558054586</v>
+        <v>334.8428558054585</v>
       </c>
     </row>
     <row r="1486">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="B1486" t="n">
-        <v>334.5453558054586</v>
+        <v>334.5453558054585</v>
       </c>
     </row>
     <row r="1487">
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>334.2478558054586</v>
+        <v>334.2478558054585</v>
       </c>
     </row>
     <row r="1488">
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>334.5453558054587</v>
+        <v>334.5453558054585</v>
       </c>
     </row>
     <row r="1489">
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="B1489" t="n">
-        <v>334.8428558054586</v>
+        <v>334.8428558054584</v>
       </c>
     </row>
     <row r="1490">
@@ -15567,7 +15567,7 @@
         </is>
       </c>
       <c r="B1514" t="n">
-        <v>545.8308122156991</v>
+        <v>545.8308122156988</v>
       </c>
     </row>
     <row r="1515">
@@ -15577,7 +15577,7 @@
         </is>
       </c>
       <c r="B1515" t="n">
-        <v>563.6147964422836</v>
+        <v>563.6147964422833</v>
       </c>
     </row>
     <row r="1516">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="B1516" t="n">
-        <v>664.0359031360776</v>
+        <v>664.0359031360774</v>
       </c>
     </row>
     <row r="1517">
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>795.2824495211222</v>
+        <v>795.282449521122</v>
       </c>
     </row>
     <row r="1518">
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="B1518" t="n">
-        <v>918.5311912802448</v>
+        <v>918.5311912802446</v>
       </c>
     </row>
     <row r="1519">
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="B1521" t="n">
-        <v>793.3482575565066</v>
+        <v>793.3482575565063</v>
       </c>
     </row>
     <row r="1522">
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="B1522" t="n">
-        <v>877.4416008894495</v>
+        <v>877.4416008894492</v>
       </c>
     </row>
     <row r="1523">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="B1523" t="n">
-        <v>985.301420626993</v>
+        <v>985.3014206269927</v>
       </c>
     </row>
     <row r="1524">
@@ -15747,7 +15747,7 @@
         </is>
       </c>
       <c r="B1532" t="n">
-        <v>1000</v>
+        <v>999.9999999999999</v>
       </c>
     </row>
     <row r="1533">
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="B1537" t="n">
-        <v>996.0436569188971</v>
+        <v>996.043656918897</v>
       </c>
     </row>
     <row r="1538">
@@ -16047,7 +16047,7 @@
         </is>
       </c>
       <c r="B1562" t="n">
-        <v>150.0776799986212</v>
+        <v>150.0776799986209</v>
       </c>
     </row>
     <row r="1563">
@@ -16057,7 +16057,7 @@
         </is>
       </c>
       <c r="B1563" t="n">
-        <v>174.4384377947779</v>
+        <v>174.4384377947777</v>
       </c>
     </row>
     <row r="1564">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="B1564" t="n">
-        <v>281.2566483365413</v>
+        <v>281.2566483365409</v>
       </c>
     </row>
     <row r="1565">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="B1565" t="n">
-        <v>415.0121018463632</v>
+        <v>415.012101846363</v>
       </c>
     </row>
     <row r="1566">
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="B1566" t="n">
-        <v>544.3606663753037</v>
+        <v>544.3606663753035</v>
       </c>
     </row>
     <row r="1567">
@@ -16117,7 +16117,7 @@
         </is>
       </c>
       <c r="B1569" t="n">
-        <v>149.6854821280921</v>
+        <v>149.6854821280918</v>
       </c>
     </row>
     <row r="1570">
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="B1570" t="n">
-        <v>180.4292984634096</v>
+        <v>180.4292984634093</v>
       </c>
     </row>
     <row r="1571">
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="B1571" t="n">
-        <v>205.085807758544</v>
+        <v>205.0858077585436</v>
       </c>
     </row>
     <row r="1572">
@@ -16227,7 +16227,7 @@
         </is>
       </c>
       <c r="B1580" t="n">
-        <v>186.4422873632726</v>
+        <v>186.4422873632725</v>
       </c>
     </row>
     <row r="1581">
@@ -16277,7 +16277,7 @@
         </is>
       </c>
       <c r="B1585" t="n">
-        <v>394.0739474375233</v>
+        <v>394.0739474375232</v>
       </c>
     </row>
     <row r="1586">
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="B1586" t="n">
-        <v>150.0776799986212</v>
+        <v>150.0776799986209</v>
       </c>
     </row>
     <row r="1587">
@@ -16297,7 +16297,7 @@
         </is>
       </c>
       <c r="B1587" t="n">
-        <v>174.4384377947779</v>
+        <v>174.4384377947777</v>
       </c>
     </row>
     <row r="1588">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="B1588" t="n">
-        <v>281.2566483365413</v>
+        <v>281.2566483365409</v>
       </c>
     </row>
     <row r="1589">
@@ -16317,7 +16317,7 @@
         </is>
       </c>
       <c r="B1589" t="n">
-        <v>415.0121018463632</v>
+        <v>415.012101846363</v>
       </c>
     </row>
     <row r="1590">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="B1590" t="n">
-        <v>544.3606663753037</v>
+        <v>544.3606663753035</v>
       </c>
     </row>
     <row r="1591">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="B1593" t="n">
-        <v>149.6854821280921</v>
+        <v>149.6854821280918</v>
       </c>
     </row>
     <row r="1594">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="B1594" t="n">
-        <v>180.4292984634096</v>
+        <v>180.4292984634093</v>
       </c>
     </row>
     <row r="1595">
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="B1595" t="n">
-        <v>205.085807758544</v>
+        <v>205.0858077585436</v>
       </c>
     </row>
     <row r="1596">
@@ -16467,7 +16467,7 @@
         </is>
       </c>
       <c r="B1604" t="n">
-        <v>186.4422873632726</v>
+        <v>186.4422873632725</v>
       </c>
     </row>
     <row r="1605">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="B1609" t="n">
-        <v>394.0739474375233</v>
+        <v>394.0739474375232</v>
       </c>
     </row>
     <row r="1610">
@@ -16527,7 +16527,7 @@
         </is>
       </c>
       <c r="B1610" t="n">
-        <v>150.0776799986212</v>
+        <v>150.0776799986209</v>
       </c>
     </row>
     <row r="1611">
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="B1611" t="n">
-        <v>174.4384377947779</v>
+        <v>174.4384377947777</v>
       </c>
     </row>
     <row r="1612">
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="B1612" t="n">
-        <v>281.2566483365413</v>
+        <v>281.2566483365409</v>
       </c>
     </row>
     <row r="1613">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="B1613" t="n">
-        <v>415.0121018463632</v>
+        <v>415.012101846363</v>
       </c>
     </row>
     <row r="1614">
@@ -16567,7 +16567,7 @@
         </is>
       </c>
       <c r="B1614" t="n">
-        <v>544.3606663753037</v>
+        <v>544.3606663753035</v>
       </c>
     </row>
     <row r="1615">
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="B1617" t="n">
-        <v>149.6854821280921</v>
+        <v>149.6854821280918</v>
       </c>
     </row>
     <row r="1618">
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="B1618" t="n">
-        <v>180.4292984634096</v>
+        <v>180.4292984634093</v>
       </c>
     </row>
     <row r="1619">
@@ -16617,7 +16617,7 @@
         </is>
       </c>
       <c r="B1619" t="n">
-        <v>205.085807758544</v>
+        <v>205.0858077585436</v>
       </c>
     </row>
     <row r="1620">
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="B1628" t="n">
-        <v>186.4422873632726</v>
+        <v>186.4422873632725</v>
       </c>
     </row>
     <row r="1629">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="B1633" t="n">
-        <v>394.0739474375233</v>
+        <v>394.0739474375232</v>
       </c>
     </row>
     <row r="1634">
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="B1658" t="n">
-        <v>120.0621439988969</v>
+        <v>120.0621439988967</v>
       </c>
     </row>
     <row r="1659">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="B1659" t="n">
-        <v>139.5507502358224</v>
+        <v>139.5507502358221</v>
       </c>
     </row>
     <row r="1660">
@@ -17027,7 +17027,7 @@
         </is>
       </c>
       <c r="B1660" t="n">
-        <v>225.005318669233</v>
+        <v>225.0053186692328</v>
       </c>
     </row>
     <row r="1661">
@@ -17037,7 +17037,7 @@
         </is>
       </c>
       <c r="B1661" t="n">
-        <v>332.0096814770906</v>
+        <v>332.0096814770903</v>
       </c>
     </row>
     <row r="1662">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="B1662" t="n">
-        <v>435.488533100243</v>
+        <v>435.4885331002428</v>
       </c>
     </row>
     <row r="1663">
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="B1665" t="n">
-        <v>119.7483857024737</v>
+        <v>119.7483857024734</v>
       </c>
     </row>
     <row r="1666">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="B1666" t="n">
-        <v>144.3434387707277</v>
+        <v>144.3434387707274</v>
       </c>
     </row>
     <row r="1667">
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="B1667" t="n">
-        <v>164.0686462068352</v>
+        <v>164.0686462068349</v>
       </c>
     </row>
     <row r="1668">
@@ -17187,7 +17187,7 @@
         </is>
       </c>
       <c r="B1676" t="n">
-        <v>149.1538298906181</v>
+        <v>149.153829890618</v>
       </c>
     </row>
     <row r="1677">
@@ -17607,7 +17607,7 @@
         </is>
       </c>
       <c r="B1718" t="n">
-        <v>231.5377197724063</v>
+        <v>252.1285846166363</v>
       </c>
     </row>
     <row r="1719">
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="B1766" t="n">
-        <v>115.7688598862031</v>
+        <v>126.0642923083182</v>
       </c>
     </row>
     <row r="1767">
@@ -18327,7 +18327,7 @@
         </is>
       </c>
       <c r="B1790" t="n">
-        <v>32.60084504392833</v>
+        <v>27.13139656967974</v>
       </c>
     </row>
     <row r="1791">
@@ -18407,7 +18407,7 @@
         </is>
       </c>
       <c r="B1798" t="n">
-        <v>44.07076801970052</v>
+        <v>36.56327631357377</v>
       </c>
     </row>
     <row r="1799">
@@ -18807,7 +18807,7 @@
         </is>
       </c>
       <c r="B1838" t="n">
-        <v>0</v>
+        <v>8.751117558797752</v>
       </c>
     </row>
     <row r="1839">
@@ -18887,7 +18887,7 @@
         </is>
       </c>
       <c r="B1846" t="n">
-        <v>0</v>
+        <v>12.01198672980279</v>
       </c>
     </row>
     <row r="1847">
@@ -19407,7 +19407,7 @@
         </is>
       </c>
       <c r="B1898" t="n">
-        <v>120.0621439988969</v>
+        <v>120.0621439988967</v>
       </c>
     </row>
     <row r="1899">
@@ -19417,7 +19417,7 @@
         </is>
       </c>
       <c r="B1899" t="n">
-        <v>139.5507502358224</v>
+        <v>139.5507502358221</v>
       </c>
     </row>
     <row r="1900">
@@ -19427,7 +19427,7 @@
         </is>
       </c>
       <c r="B1900" t="n">
-        <v>225.005318669233</v>
+        <v>225.0053186692328</v>
       </c>
     </row>
     <row r="1901">
@@ -19437,7 +19437,7 @@
         </is>
       </c>
       <c r="B1901" t="n">
-        <v>332.0096814770906</v>
+        <v>332.0096814770903</v>
       </c>
     </row>
     <row r="1902">
@@ -19447,7 +19447,7 @@
         </is>
       </c>
       <c r="B1902" t="n">
-        <v>435.488533100243</v>
+        <v>435.4885331002428</v>
       </c>
     </row>
     <row r="1903">
@@ -19477,7 +19477,7 @@
         </is>
       </c>
       <c r="B1905" t="n">
-        <v>119.7483857024737</v>
+        <v>119.7483857024734</v>
       </c>
     </row>
     <row r="1906">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="B1906" t="n">
-        <v>144.3434387707277</v>
+        <v>144.3434387707274</v>
       </c>
     </row>
     <row r="1907">
@@ -19497,7 +19497,7 @@
         </is>
       </c>
       <c r="B1907" t="n">
-        <v>164.0686462068352</v>
+        <v>164.0686462068349</v>
       </c>
     </row>
     <row r="1908">
@@ -19587,7 +19587,7 @@
         </is>
       </c>
       <c r="B1916" t="n">
-        <v>149.1538298906181</v>
+        <v>149.153829890618</v>
       </c>
     </row>
     <row r="1917">
@@ -19647,7 +19647,7 @@
         </is>
       </c>
       <c r="B1922" t="n">
-        <v>120.0621439988969</v>
+        <v>120.0621439988967</v>
       </c>
     </row>
     <row r="1923">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="B1923" t="n">
-        <v>139.5507502358224</v>
+        <v>139.5507502358221</v>
       </c>
     </row>
     <row r="1924">
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="B1924" t="n">
-        <v>225.005318669233</v>
+        <v>225.0053186692328</v>
       </c>
     </row>
     <row r="1925">
@@ -19677,7 +19677,7 @@
         </is>
       </c>
       <c r="B1925" t="n">
-        <v>332.0096814770906</v>
+        <v>332.0096814770903</v>
       </c>
     </row>
     <row r="1926">
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="B1926" t="n">
-        <v>435.488533100243</v>
+        <v>435.4885331002428</v>
       </c>
     </row>
     <row r="1927">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="B1929" t="n">
-        <v>119.7483857024737</v>
+        <v>119.7483857024734</v>
       </c>
     </row>
     <row r="1930">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="B1930" t="n">
-        <v>144.3434387707277</v>
+        <v>144.3434387707274</v>
       </c>
     </row>
     <row r="1931">
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="B1931" t="n">
-        <v>164.0686462068352</v>
+        <v>164.0686462068349</v>
       </c>
     </row>
     <row r="1932">
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="B1940" t="n">
-        <v>149.1538298906181</v>
+        <v>149.153829890618</v>
       </c>
     </row>
     <row r="1941">
@@ -21207,7 +21207,7 @@
         </is>
       </c>
       <c r="B2078" t="n">
-        <v>543.7004997738129</v>
+        <v>543.7004997738128</v>
       </c>
     </row>
     <row r="2079">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="B2082" t="n">
-        <v>298.8892769169826</v>
+        <v>298.8892769169825</v>
       </c>
     </row>
     <row r="2083">
@@ -21257,7 +21257,7 @@
         </is>
       </c>
       <c r="B2083" t="n">
-        <v>354.110135187352</v>
+        <v>354.1101351873519</v>
       </c>
     </row>
     <row r="2084">
@@ -21267,7 +21267,7 @@
         </is>
       </c>
       <c r="B2084" t="n">
-        <v>328.5489707348532</v>
+        <v>328.5489707348531</v>
       </c>
     </row>
     <row r="2085">
@@ -23607,7 +23607,7 @@
         </is>
       </c>
       <c r="B2318" t="n">
-        <v>11.89075846978224</v>
+        <v>32.48162331401227</v>
       </c>
     </row>
     <row r="2319">
@@ -23847,7 +23847,7 @@
         </is>
       </c>
       <c r="B2342" t="n">
-        <v>149.6590481053444</v>
+        <v>154.3080793084557</v>
       </c>
     </row>
     <row r="2343">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="B2346" t="n">
-        <v>69.38646004062335</v>
+        <v>69.38646004062333</v>
       </c>
     </row>
     <row r="2347">
@@ -23897,7 +23897,7 @@
         </is>
       </c>
       <c r="B2347" t="n">
-        <v>105.2743264020959</v>
+        <v>105.2743264020958</v>
       </c>
     </row>
     <row r="2348">
@@ -23907,7 +23907,7 @@
         </is>
       </c>
       <c r="B2348" t="n">
-        <v>80.38885028061306</v>
+        <v>80.38885028061307</v>
       </c>
     </row>
     <row r="2349">
@@ -23927,7 +23927,7 @@
         </is>
       </c>
       <c r="B2350" t="n">
-        <v>118.7462709505568</v>
+        <v>125.1276389007645</v>
       </c>
     </row>
     <row r="2351">
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="B2374" t="n">
-        <v>14.55047769042756</v>
+        <v>26.56246442023035</v>
       </c>
     </row>
     <row r="2375">
@@ -24207,7 +24207,7 @@
         </is>
       </c>
       <c r="B2378" t="n">
-        <v>2.617052585179026</v>
+        <v>2.617052585179025</v>
       </c>
     </row>
     <row r="2379">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="B2380" t="n">
-        <v>1.409483606919885</v>
+        <v>1.409483606919886</v>
       </c>
     </row>
     <row r="2381">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="B2394" t="n">
-        <v>1.224175098750766</v>
+        <v>1.224175098750765</v>
       </c>
     </row>
     <row r="2395">
@@ -24487,7 +24487,7 @@
         </is>
       </c>
       <c r="B2406" t="n">
-        <v>1.170923959083968</v>
+        <v>1.170923959083969</v>
       </c>
     </row>
     <row r="2407">
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="B2417" t="n">
-        <v>3.528000000000002</v>
+        <v>3.528000000000001</v>
       </c>
     </row>
     <row r="2418">
@@ -25767,7 +25767,7 @@
         </is>
       </c>
       <c r="B2534" t="n">
-        <v>149.6590481053444</v>
+        <v>154.3080793084557</v>
       </c>
     </row>
     <row r="2535">
@@ -25807,7 +25807,7 @@
         </is>
       </c>
       <c r="B2538" t="n">
-        <v>69.38646004062335</v>
+        <v>69.38646004062333</v>
       </c>
     </row>
     <row r="2539">
@@ -25817,7 +25817,7 @@
         </is>
       </c>
       <c r="B2539" t="n">
-        <v>105.2743264020959</v>
+        <v>105.2743264020958</v>
       </c>
     </row>
     <row r="2540">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="B2540" t="n">
-        <v>80.38885028061306</v>
+        <v>80.38885028061307</v>
       </c>
     </row>
     <row r="2541">
@@ -25847,7 +25847,7 @@
         </is>
       </c>
       <c r="B2542" t="n">
-        <v>118.7462709505568</v>
+        <v>125.1276389007645</v>
       </c>
     </row>
     <row r="2543">
